--- a/1차 개발 설계서/UI/05 화면 명세.xlsx
+++ b/1차 개발 설계서/UI/05 화면 명세.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'화면API연결'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'화면상태'!$A$1:$D$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'화면상태'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'화면전환'!$A$1:$E$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'화면전환'!$A$1:$E$32</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'화면전환'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'디자인토큰'!$A$1:$C$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'디자인토큰'!$1:$1</definedName>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>현재 방장</t>
+          <t>모든 현재 참여자(방장 포함)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 권한 거부</t>
+          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 동일 권한 / 비참여·탈퇴·퇴장·이용 제한 거부</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="119" customHeight="1">
+    <row r="31" ht="136" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
           <t>UI05</t>
@@ -3295,7 +3295,7 @@
         <is>
           <t>① 월~일 시작. 날짜 셀 최대 3개와 +N을 표시하고 날짜 탭으로 전체 일정을 연다.
 ② 일정 탭 → UI08로 바로 이동. 날짜를 별도 공간으로 생성하지 않는다. 취소 일정은 표시를 유지한다.
-③ 보기 방식은 기기에 보관한다. ④ 현재 방장만 UI06에서 일정을 수동 추가한다. 반복 생성은 없다. 뒤로 오면 월·선택·스크롤을 복원한다.</t>
+③ 초대·관리에서 모든 현재 참여자가 UI23에 진입한다. 보기 방식은 기기에 보관한다. ④ 현재 방장만 UI06에서 일정을 수동 추가한다. 반복 생성은 없다. 뒤로 오면 월·선택·스크롤을 복원한다.</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -3309,7 +3309,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="119" customHeight="1">
+    <row r="32" ht="136" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>UI05</t>
@@ -3334,7 +3334,7 @@
         <is>
           <t>① 월~일 시작. 날짜 셀 최대 3개와 +N을 표시하고 날짜 탭으로 전체 일정을 연다.
 ② 일정 탭 → UI08로 바로 이동. 날짜를 별도 공간으로 생성하지 않는다. 취소 일정은 표시를 유지한다.
-③ 보기 방식은 기기에 보관한다. ④ 현재 방장만 UI06에서 일정을 수동 추가한다. 반복 생성은 없다. 뒤로 오면 월·선택·스크롤을 복원한다.</t>
+③ 초대·관리에서 모든 현재 참여자가 UI23에 진입한다. 보기 방식은 기기에 보관한다. ④ 현재 방장만 UI06에서 일정을 수동 추가한다. 반복 생성은 없다. 뒤로 오면 월·선택·스크롤을 복원한다.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -3348,7 +3348,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="119" customHeight="1">
+    <row r="33" ht="136" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
           <t>UI05</t>
@@ -3373,7 +3373,7 @@
         <is>
           <t>① 월~일 시작. 날짜 셀 최대 3개와 +N을 표시하고 날짜 탭으로 전체 일정을 연다.
 ② 일정 탭 → UI08로 바로 이동. 날짜를 별도 공간으로 생성하지 않는다. 취소 일정은 표시를 유지한다.
-③ 보기 방식은 기기에 보관한다. ④ 현재 방장만 UI06에서 일정을 수동 추가한다. 반복 생성은 없다. 뒤로 오면 월·선택·스크롤을 복원한다.</t>
+③ 초대·관리에서 모든 현재 참여자가 UI23에 진입한다. 보기 방식은 기기에 보관한다. ④ 현재 방장만 UI06에서 일정을 수동 추가한다. 반복 생성은 없다. 뒤로 오면 월·선택·스크롤을 복원한다.</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -3387,7 +3387,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="119" customHeight="1">
+    <row r="34" ht="136" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>UI05</t>
@@ -3412,7 +3412,7 @@
         <is>
           <t>① 월~일 시작. 날짜 셀 최대 3개와 +N을 표시하고 날짜 탭으로 전체 일정을 연다.
 ② 일정 탭 → UI08로 바로 이동. 날짜를 별도 공간으로 생성하지 않는다. 취소 일정은 표시를 유지한다.
-③ 보기 방식은 기기에 보관한다. ④ 현재 방장만 UI06에서 일정을 수동 추가한다. 반복 생성은 없다. 뒤로 오면 월·선택·스크롤을 복원한다.</t>
+③ 초대·관리에서 모든 현재 참여자가 UI23에 진입한다. 보기 방식은 기기에 보관한다. ④ 현재 방장만 UI06에서 일정을 수동 추가한다. 반복 생성은 없다. 뒤로 오면 월·선택·스크롤을 복원한다.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="119" customHeight="1">
+    <row r="35" ht="136" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
           <t>UI05</t>
@@ -3452,7 +3452,7 @@
         <is>
           <t>① 월~일 시작. 날짜 셀 최대 3개와 +N을 표시하고 날짜 탭으로 전체 일정을 연다.
 ② 일정 탭 → UI08로 바로 이동. 날짜를 별도 공간으로 생성하지 않는다. 취소 일정은 표시를 유지한다.
-③ 보기 방식은 기기에 보관한다. ④ 현재 방장만 UI06에서 일정을 수동 추가한다. 반복 생성은 없다. 뒤로 오면 월·선택·스크롤을 복원한다.</t>
+③ 초대·관리에서 모든 현재 참여자가 UI23에 진입한다. 보기 방식은 기기에 보관한다. ④ 현재 방장만 UI06에서 일정을 수동 추가한다. 반복 생성은 없다. 뒤로 오면 월·선택·스크롤을 복원한다.</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -3466,7 +3466,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="119" customHeight="1">
+    <row r="36" ht="136" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>UI05</t>
@@ -3484,14 +3484,14 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>③ 달력 / 일정 목록   ·   모임 관리 &gt;</t>
+          <t>③ 달력 / 일정 목록  ·  초대·관리 &gt;</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
           <t>① 월~일 시작. 날짜 셀 최대 3개와 +N을 표시하고 날짜 탭으로 전체 일정을 연다.
 ② 일정 탭 → UI08로 바로 이동. 날짜를 별도 공간으로 생성하지 않는다. 취소 일정은 표시를 유지한다.
-③ 보기 방식은 기기에 보관한다. ④ 현재 방장만 UI06에서 일정을 수동 추가한다. 반복 생성은 없다. 뒤로 오면 월·선택·스크롤을 복원한다.</t>
+③ 초대·관리에서 모든 현재 참여자가 UI23에 진입한다. 보기 방식은 기기에 보관한다. ④ 현재 방장만 UI06에서 일정을 수동 추가한다. 반복 생성은 없다. 뒤로 오면 월·선택·스크롤을 복원한다.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="119" customHeight="1">
+    <row r="37" ht="136" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
           <t>UI05</t>
@@ -3530,7 +3530,7 @@
         <is>
           <t>① 월~일 시작. 날짜 셀 최대 3개와 +N을 표시하고 날짜 탭으로 전체 일정을 연다.
 ② 일정 탭 → UI08로 바로 이동. 날짜를 별도 공간으로 생성하지 않는다. 취소 일정은 표시를 유지한다.
-③ 보기 방식은 기기에 보관한다. ④ 현재 방장만 UI06에서 일정을 수동 추가한다. 반복 생성은 없다. 뒤로 오면 월·선택·스크롤을 복원한다.</t>
+③ 초대·관리에서 모든 현재 참여자가 UI23에 진입한다. 보기 방식은 기기에 보관한다. ④ 현재 방장만 UI06에서 일정을 수동 추가한다. 반복 생성은 없다. 뒤로 오면 월·선택·스크롤을 복원한다.</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -7816,7 +7816,7 @@
         </is>
       </c>
     </row>
-    <row r="147" ht="153" customHeight="1">
+    <row r="147" ht="160" customHeight="1">
       <c r="A147" s="3" t="inlineStr">
         <is>
           <t>UI23</t>
@@ -7839,23 +7839,24 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>코드 길이8자는 기술 설계안이며 기능명세의 고정 정책이 아니다. 만료는 서버 발급시각+168시간, 확인 횟수는 서버가 그 초대로 미리보기를 응답한 수이며 50회에 소진된다.
+          <t>모든 현재 참여자가 같은 모임의 초대를 조회·발급·공유·복사·취소한다. 발급자 본인 여부는 관리 권한의 기준이 아니다. 참여 종료·모임 종료·이용 제한은 서버가 재검증한다.
+코드 길이8자는 기술 설계안이며 기능명세의 고정 정책이 아니다. 만료는 서버 발급시각+168시간, 확인 횟수는 서버가 그 초대로 미리보기를 응답한 수이며 50회에 소진된다.
 ② 모임명·요약·링크·코드만 공유. 공유 취소는 초대 취소가 아니다. 상태는 사용 가능·소진·만료·취소로 구분한다.
 ④ 새 발급은 기존 초대를 유지하고 횟수는 0부터 시작한다. 같은 요청 재시도는 동일 초대. 참여 확정은 횟수를 소모하지 않으며 소진·취소는 기존 참여자에게 영향이 없다.</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>현재 방장</t>
+          <t>모든 현재 참여자(방장 포함)</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 권한 거부</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="153" customHeight="1">
+          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 동일 권한 / 비참여·탈퇴·퇴장·이용 제한 거부</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="160" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
           <t>UI23</t>
@@ -7878,23 +7879,24 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>코드 길이8자는 기술 설계안이며 기능명세의 고정 정책이 아니다. 만료는 서버 발급시각+168시간, 확인 횟수는 서버가 그 초대로 미리보기를 응답한 수이며 50회에 소진된다.
+          <t>모든 현재 참여자가 같은 모임의 초대를 조회·발급·공유·복사·취소한다. 발급자 본인 여부는 관리 권한의 기준이 아니다. 참여 종료·모임 종료·이용 제한은 서버가 재검증한다.
+코드 길이8자는 기술 설계안이며 기능명세의 고정 정책이 아니다. 만료는 서버 발급시각+168시간, 확인 횟수는 서버가 그 초대로 미리보기를 응답한 수이며 50회에 소진된다.
 ② 모임명·요약·링크·코드만 공유. 공유 취소는 초대 취소가 아니다. 상태는 사용 가능·소진·만료·취소로 구분한다.
 ④ 새 발급은 기존 초대를 유지하고 횟수는 0부터 시작한다. 같은 요청 재시도는 동일 초대. 참여 확정은 횟수를 소모하지 않으며 소진·취소는 기존 참여자에게 영향이 없다.</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>현재 방장</t>
+          <t>모든 현재 참여자(방장 포함)</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 권한 거부</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="153" customHeight="1">
+          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 동일 권한 / 비참여·탈퇴·퇴장·이용 제한 거부</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="160" customHeight="1">
       <c r="A149" s="3" t="inlineStr">
         <is>
           <t>UI23</t>
@@ -7918,23 +7920,24 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>코드 길이8자는 기술 설계안이며 기능명세의 고정 정책이 아니다. 만료는 서버 발급시각+168시간, 확인 횟수는 서버가 그 초대로 미리보기를 응답한 수이며 50회에 소진된다.
+          <t>모든 현재 참여자가 같은 모임의 초대를 조회·발급·공유·복사·취소한다. 발급자 본인 여부는 관리 권한의 기준이 아니다. 참여 종료·모임 종료·이용 제한은 서버가 재검증한다.
+코드 길이8자는 기술 설계안이며 기능명세의 고정 정책이 아니다. 만료는 서버 발급시각+168시간, 확인 횟수는 서버가 그 초대로 미리보기를 응답한 수이며 50회에 소진된다.
 ② 모임명·요약·링크·코드만 공유. 공유 취소는 초대 취소가 아니다. 상태는 사용 가능·소진·만료·취소로 구분한다.
 ④ 새 발급은 기존 초대를 유지하고 횟수는 0부터 시작한다. 같은 요청 재시도는 동일 초대. 참여 확정은 횟수를 소모하지 않으며 소진·취소는 기존 참여자에게 영향이 없다.</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>현재 방장</t>
+          <t>모든 현재 참여자(방장 포함)</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 권한 거부</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="153" customHeight="1">
+          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 동일 권한 / 비참여·탈퇴·퇴장·이용 제한 거부</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="160" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
           <t>UI23</t>
@@ -7957,23 +7960,24 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>코드 길이8자는 기술 설계안이며 기능명세의 고정 정책이 아니다. 만료는 서버 발급시각+168시간, 확인 횟수는 서버가 그 초대로 미리보기를 응답한 수이며 50회에 소진된다.
+          <t>모든 현재 참여자가 같은 모임의 초대를 조회·발급·공유·복사·취소한다. 발급자 본인 여부는 관리 권한의 기준이 아니다. 참여 종료·모임 종료·이용 제한은 서버가 재검증한다.
+코드 길이8자는 기술 설계안이며 기능명세의 고정 정책이 아니다. 만료는 서버 발급시각+168시간, 확인 횟수는 서버가 그 초대로 미리보기를 응답한 수이며 50회에 소진된다.
 ② 모임명·요약·링크·코드만 공유. 공유 취소는 초대 취소가 아니다. 상태는 사용 가능·소진·만료·취소로 구분한다.
 ④ 새 발급은 기존 초대를 유지하고 횟수는 0부터 시작한다. 같은 요청 재시도는 동일 초대. 참여 확정은 횟수를 소모하지 않으며 소진·취소는 기존 참여자에게 영향이 없다.</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>현재 방장</t>
+          <t>모든 현재 참여자(방장 포함)</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 권한 거부</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="153" customHeight="1">
+          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 동일 권한 / 비참여·탈퇴·퇴장·이용 제한 거부</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="160" customHeight="1">
       <c r="A151" s="3" t="inlineStr">
         <is>
           <t>UI23</t>
@@ -7996,23 +8000,24 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>코드 길이8자는 기술 설계안이며 기능명세의 고정 정책이 아니다. 만료는 서버 발급시각+168시간, 확인 횟수는 서버가 그 초대로 미리보기를 응답한 수이며 50회에 소진된다.
+          <t>모든 현재 참여자가 같은 모임의 초대를 조회·발급·공유·복사·취소한다. 발급자 본인 여부는 관리 권한의 기준이 아니다. 참여 종료·모임 종료·이용 제한은 서버가 재검증한다.
+코드 길이8자는 기술 설계안이며 기능명세의 고정 정책이 아니다. 만료는 서버 발급시각+168시간, 확인 횟수는 서버가 그 초대로 미리보기를 응답한 수이며 50회에 소진된다.
 ② 모임명·요약·링크·코드만 공유. 공유 취소는 초대 취소가 아니다. 상태는 사용 가능·소진·만료·취소로 구분한다.
 ④ 새 발급은 기존 초대를 유지하고 횟수는 0부터 시작한다. 같은 요청 재시도는 동일 초대. 참여 확정은 횟수를 소모하지 않으며 소진·취소는 기존 참여자에게 영향이 없다.</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>현재 방장</t>
+          <t>모든 현재 참여자(방장 포함)</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 권한 거부</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="153" customHeight="1">
+          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 동일 권한 / 비참여·탈퇴·퇴장·이용 제한 거부</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="160" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
           <t>UI23</t>
@@ -8036,23 +8041,24 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>코드 길이8자는 기술 설계안이며 기능명세의 고정 정책이 아니다. 만료는 서버 발급시각+168시간, 확인 횟수는 서버가 그 초대로 미리보기를 응답한 수이며 50회에 소진된다.
+          <t>모든 현재 참여자가 같은 모임의 초대를 조회·발급·공유·복사·취소한다. 발급자 본인 여부는 관리 권한의 기준이 아니다. 참여 종료·모임 종료·이용 제한은 서버가 재검증한다.
+코드 길이8자는 기술 설계안이며 기능명세의 고정 정책이 아니다. 만료는 서버 발급시각+168시간, 확인 횟수는 서버가 그 초대로 미리보기를 응답한 수이며 50회에 소진된다.
 ② 모임명·요약·링크·코드만 공유. 공유 취소는 초대 취소가 아니다. 상태는 사용 가능·소진·만료·취소로 구분한다.
 ④ 새 발급은 기존 초대를 유지하고 횟수는 0부터 시작한다. 같은 요청 재시도는 동일 초대. 참여 확정은 횟수를 소모하지 않으며 소진·취소는 기존 참여자에게 영향이 없다.</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>현재 방장</t>
+          <t>모든 현재 참여자(방장 포함)</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 권한 거부</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="153" customHeight="1">
+          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 동일 권한 / 비참여·탈퇴·퇴장·이용 제한 거부</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="160" customHeight="1">
       <c r="A153" s="3" t="inlineStr">
         <is>
           <t>UI23</t>
@@ -8075,23 +8081,24 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>코드 길이8자는 기술 설계안이며 기능명세의 고정 정책이 아니다. 만료는 서버 발급시각+168시간, 확인 횟수는 서버가 그 초대로 미리보기를 응답한 수이며 50회에 소진된다.
+          <t>모든 현재 참여자가 같은 모임의 초대를 조회·발급·공유·복사·취소한다. 발급자 본인 여부는 관리 권한의 기준이 아니다. 참여 종료·모임 종료·이용 제한은 서버가 재검증한다.
+코드 길이8자는 기술 설계안이며 기능명세의 고정 정책이 아니다. 만료는 서버 발급시각+168시간, 확인 횟수는 서버가 그 초대로 미리보기를 응답한 수이며 50회에 소진된다.
 ② 모임명·요약·링크·코드만 공유. 공유 취소는 초대 취소가 아니다. 상태는 사용 가능·소진·만료·취소로 구분한다.
 ④ 새 발급은 기존 초대를 유지하고 횟수는 0부터 시작한다. 같은 요청 재시도는 동일 초대. 참여 확정은 횟수를 소모하지 않으며 소진·취소는 기존 참여자에게 영향이 없다.</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>현재 방장</t>
+          <t>모든 현재 참여자(방장 포함)</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 권한 거부</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="153" customHeight="1">
+          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 동일 권한 / 비참여·탈퇴·퇴장·이용 제한 거부</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="160" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
           <t>UI23</t>
@@ -8114,19 +8121,20 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>코드 길이8자는 기술 설계안이며 기능명세의 고정 정책이 아니다. 만료는 서버 발급시각+168시간, 확인 횟수는 서버가 그 초대로 미리보기를 응답한 수이며 50회에 소진된다.
+          <t>모든 현재 참여자가 같은 모임의 초대를 조회·발급·공유·복사·취소한다. 발급자 본인 여부는 관리 권한의 기준이 아니다. 참여 종료·모임 종료·이용 제한은 서버가 재검증한다.
+코드 길이8자는 기술 설계안이며 기능명세의 고정 정책이 아니다. 만료는 서버 발급시각+168시간, 확인 횟수는 서버가 그 초대로 미리보기를 응답한 수이며 50회에 소진된다.
 ② 모임명·요약·링크·코드만 공유. 공유 취소는 초대 취소가 아니다. 상태는 사용 가능·소진·만료·취소로 구분한다.
 ④ 새 발급은 기존 초대를 유지하고 횟수는 0부터 시작한다. 같은 요청 재시도는 동일 초대. 참여 확정은 횟수를 소모하지 않으며 소진·취소는 기존 참여자에게 영향이 없다.</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>현재 방장</t>
+          <t>모든 현재 참여자(방장 포함)</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 권한 거부</t>
+          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 동일 권한 / 비참여·탈퇴·퇴장·이용 제한 거부</t>
         </is>
       </c>
     </row>
@@ -13342,7 +13350,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 권한 거부</t>
+          <t>발급 실패·결과 불명 / 취소·만료·소진 / 정원10명 / 일반 참여자 동일 권한 / 비참여·탈퇴·퇴장·이용 제한 거부</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -13629,7 +13637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -13836,12 +13844,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>UI06</t>
+          <t>UI23</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>일정추가</t>
+          <t>초대 발급·관리</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -13851,7 +13859,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>현재 방장·반복 없음</t>
+          <t>모든 현재 참여자·같은 모임 초대</t>
         </is>
       </c>
     </row>
@@ -13863,12 +13871,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>UI08</t>
+          <t>UI06</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>일정선택</t>
+          <t>일정추가</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -13878,34 +13886,34 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>날짜별 화면 경유없음</t>
+          <t>현재 방장·반복 없음</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>UI05</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>UI08</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>UI09</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>공동기록</t>
+          <t>일정선택</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>tab</t>
+          <t>push</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>필터·보기방식·스크롤 유지</t>
+          <t>날짜별 화면 경유없음</t>
         </is>
       </c>
     </row>
@@ -13917,22 +13925,22 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>UI13</t>
+          <t>UI09</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>장소선택</t>
+          <t>공동기록</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>tab</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>사람별/시간순 보기</t>
+          <t>필터·보기방식·스크롤 유지</t>
         </is>
       </c>
     </row>
@@ -13944,12 +13952,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>UI10</t>
+          <t>UI13</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>장소추가</t>
+          <t>장소선택</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -13959,24 +13967,24 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>일정/방문일 전달·15개 검사</t>
+          <t>사람별/시간순 보기</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>UI08</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>UI10</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>UI11</t>
-        </is>
-      </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>직접등록</t>
+          <t>장소추가</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -13986,132 +13994,132 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>검색어 초깃값</t>
+          <t>일정/방문일 전달·15개 검사</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>UI10/UI11</t>
+          <t>UI10</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>UI08</t>
+          <t>UI11</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>방문저장성공</t>
+          <t>직접등록</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>pop</t>
+          <t>push</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>마지막순서 추가·예정 시각</t>
+          <t>검색어 초깃값</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>UI10/UI11</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
           <t>UI08</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>UI12</t>
-        </is>
-      </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>계획편집</t>
+          <t>방문저장성공</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>pop</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>미저장이탈확인</t>
+          <t>마지막순서 추가·예정 시각</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>UI08/UI13</t>
+          <t>UI08</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>UI14</t>
+          <t>UI12</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>올리기</t>
+          <t>계획편집</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>push</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>취소/만료검증</t>
+          <t>미저장이탈확인</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>UI08/UI13</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
           <t>UI14</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>UI15</t>
-        </is>
-      </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>촬영</t>
+          <t>올리기</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>sheet</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>필요시권한</t>
+          <t>취소/만료검증</t>
         </is>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>UI14/UI15</t>
+          <t>UI14</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>UI16</t>
+          <t>UI15</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>파일선택/사용</t>
+          <t>촬영</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -14121,24 +14129,24 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>최대120</t>
+          <t>필요시권한</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>UI14/UI15</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>UI16</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>UI17</t>
-        </is>
-      </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>업로드확인</t>
+          <t>파일선택/사용</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -14148,24 +14156,24 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>서버접수·한도 파일별 거부</t>
+          <t>최대120</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>UI09/UI13/UI22</t>
+          <t>UI16</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>UI18</t>
+          <t>UI17</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>카드열기</t>
+          <t>업로드확인</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -14175,7 +14183,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>공동/본인context</t>
+          <t>서버접수·한도 파일별 거부</t>
         </is>
       </c>
     </row>
@@ -14187,157 +14195,157 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>UI16</t>
+          <t>UI18</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>길게누르기/선택</t>
+          <t>카드열기</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>mode</t>
+          <t>push</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>최대120·기존 기록 선택(구 UI19)</t>
+          <t>공동/본인context</t>
         </is>
       </c>
     </row>
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>UI09/UI13/UI22</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>UI16</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>UI20</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>본인정보수정</t>
+          <t>길게누르기/선택</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>같은일정본인</t>
+          <t>최대120·기존 기록 선택(구 UI19)</t>
         </is>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>UI18/UI16</t>
+          <t>UI16</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>UI21</t>
+          <t>UI20</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>휴대폰 저장</t>
+          <t>본인정보수정</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>push</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>현재참여·공유 없음</t>
+          <t>같은일정본인</t>
         </is>
       </c>
     </row>
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>UI28</t>
+          <t>UI18/UI16</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>UI22</t>
+          <t>UI21</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>내기록</t>
+          <t>휴대폰 저장</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>sheet</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>나간모임본인포함</t>
+          <t>현재참여·공유 없음</t>
         </is>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>UI26</t>
+          <t>UI28</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>UI27</t>
+          <t>UI22</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>나가기</t>
+          <t>내기록</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>push</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>방장선행조건</t>
+          <t>나간모임본인포함</t>
         </is>
       </c>
     </row>
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>UI28</t>
+          <t>UI26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>UI30</t>
+          <t>UI27</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>계정삭제</t>
+          <t>나가기</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>sheet</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>재인증·역할정리</t>
+          <t>방장선행조건</t>
         </is>
       </c>
     </row>
@@ -14349,12 +14357,12 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>UI29</t>
+          <t>UI30</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>로그인수단</t>
+          <t>계정삭제</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -14364,78 +14372,78 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>명시적연결</t>
+          <t>재인증·역할정리</t>
         </is>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>UI31</t>
+          <t>UI28</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>UI28</t>
+          <t>UI29</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>차단해제/신고조회</t>
+          <t>로그인수단</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>pop</t>
+          <t>push</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>목록/집계갱신</t>
+          <t>명시적연결</t>
         </is>
       </c>
     </row>
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>UI26</t>
+          <t>UI31</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>UI32</t>
+          <t>UI28</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>부재복구문의</t>
+          <t>차단해제/신고조회</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>push</t>
+          <t>pop</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>후임별도동의</t>
+          <t>목록/집계갱신</t>
         </is>
       </c>
     </row>
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>UI28</t>
+          <t>UI26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>UI33</t>
+          <t>UI32</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>캐시/저장공간</t>
+          <t>부재복구문의</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -14445,39 +14453,66 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>원본과캐시분리</t>
+          <t>후임별도동의</t>
         </is>
       </c>
     </row>
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
+          <t>UI28</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>UI33</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>캐시/저장공간</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>원본과캐시분리</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>모든쓰기화면</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>UI35</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>결과불명/충돌</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>inline/sheet</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>입력유지·작업조회</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E31"/>
+  <autoFilter ref="A1:E32"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
